--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_04_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_04_19_Cau.xlsx
@@ -675,7 +675,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo dõi dữ liệu từ sự kiện tới một thay đổi đã được kiểm chứng.</t>
+          <t>Ứng dụng có 1 triệu lượt dùng và ghi log mọi prompt nhưng không dùng được để cải thiện sản phẩm vì vòng phản hồi bị gãy ở khâu: Thiếu tín hiệu chẩn đoán liên quan (labeled feedback/error signal) và thiếu đường ống đưa dữ liệu vào quy trình cải thiện.</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dữ liệu phải trả lời được lỗi nào, thuộc phạm vi pháp lý/thời điểm nào và ai xác nhận.</t>
+          <t>Dữ liệu chất lượng cao để đánh giá và cải thiện trợ lý pháp lý Việt Nam: Văn bản pháp luật hiện hành có thời điểm ban hành và nguồn gốc rõ ràng (a), Các tình huống thực tế được luật sư gắn nhãn chuẩn (b), và Dữ liệu chỉnh sửa trước/sau từ chuyên gia kiểm tra (d).</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chi phí kiểm tra của con người là chi phí kỳ vọng: xác suất × chi phí khi xảy ra.</t>
+          <t>Chi phí biến đổi kỳ vọng cho mỗi kết quả = (3 lần gọi model × 0,02 USD) + (1 lần gọi tool × 0,01 USD) + (10% xác suất kiểm tra của con người × 0,50 USD) = 0,06 + 0,01 + 0,05 = 0,12 USD.</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đánh dấu ba lớp can thiệp đã có: phát hiện, khôi phục, kiểm chứng. Tìm lớp còn trống.</t>
+          <t>Hệ thống phát hiện lỗi schema và chặn cứng nhưng HR không thể tiếp tục công việc, cho thấy hệ thống thiếu lớp can thiệp khôi phục (recovery intervention): Cần thêm cách khôi phục cho HR bằng cách cho phép nhập/sửa trường hoặc từ chối xử lý, đồng thời lưu dấu vết chỉnh sửa.</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách điều được mô phỏng và quan sát khỏi hệ thống tự động ở phía sau chưa tồn tại.</t>
+          <t>Trong thử nghiệm Wizard-of-Oz, người vận hành thủ công tạo biên bản họp đạt 30/40; kết luận được hỗ trợ trực tiếp là quy trình làm việc và chất lượng đầu ra cho thấy giá trị với người dùng, nhưng chưa chứng minh mô hình tự động phía sau sẽ đạt chất lượng tương đương.</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bảng có thể chưa đủ luồng, nhưng mỗi trạng thái phải trung thực về điều đã quan sát.</t>
+          <t>Bản phân tích sản phẩm trung thực phải ghi nhận rõ ràng: Ghi 2 luồng đã trực tiếp quan sát kèm tài liệu đầu ra; đánh dấu luồng độ tin cậy thấp và việc chỉnh sửa là chưa quan sát được, đồng thời nêu rõ đầu vào/bằng chứng cần thử nghiệm thêm.</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo luồng từ đầu vào thiếu đến hành động không thể đảo ngược; mỗi chỗ người dùng cần quyền quyết định phải có trạng thái rõ.</t>
+          <t>Để luồng gửi thư an toàn và đáp ứng quy ước: Thêm trạng thái hỏi hạn chót trước khi tạo bản nháp nếu thiếu dữ kiện (a), Thêm trạng thái cho phép người dùng xem lại, chỉnh sửa hoặc hủy bản nháp (b), và Thêm trạng thái bắt buộc xác nhận người nhận và nội dung trước khi thực thi gửi (c).</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Viết riêng tổng lợi ích theo số kết quả được chấp nhận và tổng chi phí theo số yêu cầu.</t>
+          <t>Lợi ích ròng = Tổng lợi ích của các kết quả được chấp nhận − Tổng chi phí phát sinh trên toàn bộ yêu cầu: 1.000 × 0,40 × 3 − 1.000 × 0,50 = 1.200 − 500 = 700 USD.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_04_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_04_19_Cau.xlsx
@@ -624,10 +624,22 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm bước ngay sau bảng điều khiển chưa có đầu ra cho người phụ trách kế tiếp.
-Phân tích theo nguyên lý thiết kế: Tìm bước ngay sau bảng điều khiển chưa có đầu ra cho người phụ trách kế tiếp.</t>
+- 1.0 điểm: Truy vết chính xác vòng lặp hiện tại và chỉ ra điểm đứt gãy sau bước xem bảng điều khiển.
+- 1.0 điểm: Xác định đúng bước bàn giao bị thiếu: Triage phân tích nguyên nhân gốc rễ từ số liệu thô thành bài toán kỹ thuật.
+- 1.0 điểm: Chỉ định rõ người phụ trách phù hợp (AI Product Manager / AI Ops Specialist).
+- 1.0 điểm: Đề xuất tài liệu đầu ra cụ thể, khả thi (Weekly Error Triage Spec với các mẫu lỗi và đề xuất sửa prompt).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Truy vết Vòng phản hồi Hiện tại (Current Feedback Loop Trace):
+Khách hàng bấm nút Dislike (Không thích) → Sự kiện telemetry được ghi nhận vào cơ sở dữ liệu → Bảng điều khiển (Dashboard) vẽ biểu đồ đếm tổng số lượt Dislike → Đội ngũ phát triển nhìn vào biểu đồ đếm số lượt và... DỪNG LẠI Ở ĐÂY. Vòng lặp bị đứt gãy hoàn toàn tại điểm này, không có bất kỳ hành động nào chuyển tiếp sang mã nguồn hay dữ liệu.
+2. Chỉ ra Bước bàn giao đầu tiên bị thiếu (First Missing Handoff Step):
+- Bước thiếu: Bước chuyển giao từ 'Số liệu thống kê thô trên Dashboard' sang 'Phân tích nguyên nhân gốc rễ và Đóng gói bài toán cải tiến' (Root Cause Triage &amp; Actionable Backlog Handoff). Bảng điều khiển chỉ cho biết 'có bao nhiêu người không thích' chứ không cho biết 'họ không thích ở điểm nào, tại sao không thích, và kỹ sư cần sửa prompt/dữ liệu ra sao'.
+3. Đề xuất Tài liệu đầu ra và Người phụ trách để hoàn tất bước bàn giao:
+- Người phụ trách: AI Product Manager (hoặc AI Operations Specialist / Data Curator).
+- Tài liệu đầu ra bắt buộc: 'Hồ sơ Phân tích Lỗi và Đề xuất Thay đổi' (Weekly Error Triage Report &amp; Bug Spec). Tài liệu này gồm: 20 mẫu câu bị Dislike điển hình được phân loại theo nhóm lỗi cụ thể (ảo giác, cộc lốc, sai format), đi kèm chỉ số tổn thất và bản đề xuất chỉnh sửa cụ thể cho System Prompt hoặc Tool Schema gửi trực tiếp cho Kỹ sư AI đưa vào sprint tiếp theo.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một vòng phản hồi (Feedback Loop) chỉ thực sự tồn tại khi dữ liệu từ người dùng dẫn đến sự thay đổi có thể kiểm chứng trong sản phẩm. Bảng điều khiển (Dashboard) chỉ là công cụ quan sát thụ động. Nếu thiếu bước Triage chuyển hóa dữ liệu Dislike thành tài liệu đặc tả lỗi cho kỹ sư, chất lượng của hệ thống AI sẽ vĩnh viễn dậm chân tại chỗ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Continuous Improvement in AI Systems &amp; Andrew Ng - Data-Centric AI Development Workflows (https://www.deeplearning.ai/the-batch/data-centric-ai/)</t>
         </is>
       </c>
     </row>
@@ -708,10 +720,27 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nhiều dữ liệu không cứu được vòng nếu dữ liệu không liên quan tới lỗi.
-Phân tích theo nguyên lý thiết kế: Nhiều dữ liệu không cứu được vòng nếu dữ liệu không liên quan tới lỗi.</t>
+- 1.0 điểm: Chẩn đoán chính xác liên kết gãy 1: Mất người dùng dẫn đến cạn kiệt dữ liệu chỉnh sửa thực tế.
+- 1.0 điểm: Chẩn đoán chính xác liên kết gãy 2: Dữ liệu tổng hợp bị ngắt kết nối với các lỗi thực tế của sản phẩm.
+- 1.0 điểm: Đề xuất giải pháp khắc phục có mồi chuyên gia (bootstrapping) và sinh dữ liệu nhắm đúng mục tiêu lỗi.
+- 1.0 điểm: Thiết lập các chỉ số định lượng đo lường phục hồi cụ thể (Success rate &gt;= 80%, giảm lỗi &gt;= 70%).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán Hai liên kết bị gãy trong Bánh đà Dữ liệu (Data Flywheel Break Diagnosis):
+- Liên kết gãy 1: 'Sử dụng Sản phẩm → Thu thập Dữ liệu Chỉnh sửa thật' (Usage-to-Data Link Broken).
+  + Bản chất: Vì chất lượng ban đầu quá kém, người dùng bỏ rơi sản phẩm. Khi không có người dùng tương tác, hệ thống hoàn toàn cạn kiệt dữ liệu chỉnh sửa thực tế (Real User Correction Data). Vòng lặp bị triệt tiêu ngay từ nguồn cấp dữ liệu tự nhiên.
+- Liên kết gãy 2: 'Bổ sung Dữ liệu → Khắc phục Lỗi thật của Sản phẩm' (Data-to-Quality Improvement Link Broken).
+  + Bản chất: Đội ngũ cố gắng bù đắp bằng cách nạp một khối lượng lớn dữ liệu tổng hợp (Synthetic Data) tạo ngẫu nhiên nhưng các dữ liệu này lại hoàn toàn không liên quan và không mô phỏng đúng các mẫu lỗi thực tế mà người dùng từng gặp phải. Kết quả là mô hình học thêm dữ liệu rác mà các lỗi nghiêm trọng vẫn giữ nguyên.
+2. Đề xuất Cách khắc phục có kèm Chỉ số đo lường (Measurable Remediation):
+- Khắc phục Liên kết 1 (Mồi bánh đà bằng Chuyên gia / Concierge Data Bootstrapping):
+  + Giải pháp: Thuê chuyên viên nghiệp vụ (Domain Experts) trực tiếp thao tác và chỉnh sửa trên 200 tình huống sử dụng thực tế để tạo ra bộ dữ liệu chỉnh sửa mẫu chất lượng cao (Seed Gold Dataset) nhằm đưa chất lượng sản phẩm vượt ngưỡng sử dụng cơ bản.
+  + Chỉ số đo lường: Điểm chất lượng đầu ra ban đầu (Task Success Rate) tăng từ mức &lt;50% lên &gt;= 80% trước khi mở lại cho người dùng.
+- Khắc phục Liên kết 2 (Tạo Dữ liệu Tổng hợp có Định hướng Lỗi - Error-Targeted Synthetic Generation):
+  + Giải pháp: Thay vì sinh dữ liệu tổng hợp chung chung, chỉ tạo dữ liệu tổng hợp xoay quanh đúng các cụm lỗi thực tế đã được phân loại (Error-conditioned Data Augmentation).
+  + Chỉ số đo lường: Tỷ lệ lỗi lặp lại trên các tình huống đã định danh (Recurrent Error Rate) giảm &gt;= 70%.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Bánh đà dữ liệu (Data Flywheel) thường sụp đổ khi rơi vào 'vòng xoáy tử thần': Sản phẩm kém -&gt; Ít người dùng -&gt; Thiếu dữ liệu -&gt; Không cải thiện được. Ảo tưởng rằng dữ liệu tổng hợp vô định hướng có thể cứu vãn bánh đà là sai lầm phổ biến. Bắt buộc phải mồi bánh đà bằng dữ liệu chuyên gia và nhắm trúng các mẫu lỗi thực tế.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Chip Huyen - Designing Machine Learning Systems &amp; The Anatomy of the AI Data Flywheel (A16Z) (https://huyenchip.com/machine-learning-systems-design/)</t>
         </is>
       </c>
     </row>
@@ -796,10 +825,27 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nêu vì sao dữ liệu này giúp chẩn đoán tốt hơn lượt nhấp hoặc văn bản web chung chung.
-Phân tích theo nguyên lý thiết kế: Nêu vì sao dữ liệu này giúp chẩn đoán tốt hơn lượt nhấp hoặc văn bản web chung chung.</t>
+- 1.0 điểm: Chọn đúng loại dữ liệu có giá trị cao: Khai báo ràng buộc ăn kiêng chủ động của người dùng.
+- 1.0 điểm: Liệt kê đầy đủ metadata nguồn gốc cần lưu (loại ăn chay, mức độ nghiêm ngặt, timestamp, nguồn form).
+- 1.0 điểm: Phân tích sâu sắc sự vượt trội so với lượt nhấp (clicks bị nhiễu do tò mò hình ảnh, không phản ánh nhu cầu ăn thật).
+- 1.0 điểm: Nêu rõ phương pháp kiểm chứng xung đột và giới hạn về tính biến động sở thích theo thời gian.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Loại dữ liệu có Giá trị Cao (High-Value Data Selection):
+- Loại dữ liệu được chọn: Dữ liệu Hồ sơ Ràng buộc Ăn kiêng do Người dùng Tự xác nhận (Explicit User Dietary Profile &amp; Constraint Directives) kết hợp với Lịch sử Đổi món / Bỏ qua món mặn (Explicit Recipe Swap / Rejection Events).
+2. Nguồn gốc và Metadata cần lưu giữ (Data Lineage &amp; Provenance Metadata):
+- Nguồn gốc: Form khảo sát thiết lập khẩu vị của tài khoản người dùng (`onboarding_dietary_settings`) và nút bấm 'Tôi ăn chay' được lưu với cờ xác thực cao nhất.
+- Metadata cần lưu: `user_id`, `dietary_type: 'VEGAN' / 'VEGETARIAN'`, `strictness_level: 'STRICT'` (không ăn cả trứng/sữa hay chỉ kiêng thịt), `verified_at_timestamp`, `source_action: 'USER_PROFILE_SETTING'`.
+3. Phương pháp Kiểm chứng tính Xác thực của Dữ liệu:
+- Kiểm chứng bằng Hợp đồng Dữ liệu (Schema Constraint Verification): Khi người dùng gắn nhãn ăn chay, hệ thống chạy một bài test kiểm tra ngược trên các món người dùng đã lưu hoặc đánh giá 5 sao trong quá khứ để phát hiện xung đột sở thích (Preference Conflict Detection).
+4. Vì sao dữ liệu này vượt trội hơn Lượt nhấp hoặc Văn bản Web chung chung:
+- Lượt nhấp chuột (Clicks) mang tính nhiễu loạn cực cao: Người ăn chay có thể nhấp vào một hình ảnh món thịt nướng đơn thuần vì bức ảnh đẹp mắt hoặc xem cho người thân, nhưng hoàn toàn không thể ăn món đó. Suy diễn sở thích từ lượt nhấp sẽ làm hệ thống gợi ý sai lệch nghiêm trọng.
+- Văn bản web chung chung chỉ dạy mô hình kiến thức lý thuyết về món ăn, không cung cấp thông tin về ràng buộc thể trạng của từng cá nhân cụ thể.
+5. Giới hạn cần lưu ý (Boundary Limitation):
+Sở thích ăn chay của người dùng có thể thay đổi linh hoạt theo thời gian (ví dụ: ăn chay bán phần vào ngày rằm/mùng một, hoặc chuyển chế độ ăn). Dữ liệu này cần có cơ chế làm mới định kỳ (Freshness prompt) sau mỗi 3 tháng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Dữ liệu có giá trị cao nhất trong hệ thống cá nhân hóa AI là Dữ liệu tuyên bố rõ ràng từ người dùng (Explicit First-Party Declared Data), chứ không phải các tín hiệu hành vi ngầm định đầy nhiễu như lượt nhấp chuột (Implicit Clicks). Việc tôn trọng các ràng buộc cứng về ăn kiêng giúp ngăn chặn hoàn toàn các gợi ý phản cảm và bảo vệ sức khỏe người dùng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Personalization + Data Quality &amp; Recommender Systems Handbook (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -881,10 +927,27 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi giai đoạn phải có một kết luận mà nó không được phép hỗ trợ.
-Phân tích theo nguyên lý thiết kế: Mỗi giai đoạn phải có một kết luận mà nó không được phép hỗ trợ.</t>
+- 1.0 điểm: Thiết lập đầy đủ 3 giai đoạn đánh giá tuần tự (Offline eval hôm nay, Canary pilot ngày mai, Online monitoring sau đó).
+- 1.0 điểm: Nêu rõ phương pháp và mục tiêu kỹ thuật cụ thể của từng giai đoạn.
+- 1.0 điểm: Chỉ ra dứt khoát kết luận bị cấm của Giai đoạn 1 (không được kết luận người dùng thật yêu thích).
+- 1.0 điểm: Chỉ ra dứt khoát kết luận bị cấm của Giai đoạn 2 (không được kết luận sản phẩm sẵn sàng scale toàn diện).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Chuỗi Đánh giá Tối thiểu từ Hôm nay đến Sau Thử nghiệm Hạn chế (Evaluation Chain &amp; Stage Boundaries):
+1. Giai đoạn 1: Đánh giá Offline trên Bộ Test Chuẩn (Hôm nay - Pre-release Offline Eval)
+- Phương pháp: Chạy prompt mới trên Bộ dữ liệu Golden Dataset cố định gồm 50 ca kiểm thử đã được chuẩn hóa.
+- Mục đích: Kiểm tra xem prompt mới có cải thiện độ chính xác trên các ca lỗi cũ và có phát sinh lỗi hồi quy (regression) trên các ca chuẩn hay không.
+- GIỚI HẠN KẾT LUẬN TUYỆT ĐỐI KHÔNG ĐƯỢC PHÉP HỖ TRỢ: Giai đoạn này KHÔNG ĐƯỢC PHÉP kết luận rằng 'Người dùng thực tế sẽ yêu thích và tương tác nhiều hơn với tính năng này' (chưa có người dùng thật, mới chỉ là kiểm tra kỹ thuật).
+2. Giai đoạn 2: Đánh giá Thử nghiệm Hạn chế / Dogfooding (Ngày mai - Limited Pilot / Canary Run)
+- Phương pháp: Triển khai tính năng cho một nhóm nhỏ 20 người dùng nội bộ hoặc người dùng thân thiết trong 24 giờ.
+- Mục đích: Đo lường khả năng xử lý các câu hỏi thực tế đa dạng ngoài kịch bản và phát hiện các lỗi crash, lỗi format hoặc phản hồi phản cảm chưa từng thấy trong bộ offline test.
+- GIỚI HẠN KẾT LUẬN TUYỆT ĐỐI KHÔNG ĐƯỢC PHÉP HỖ TRỢ: Giai đoạn này KHÔNG ĐƯỢC PHÉP kết luận rằng 'Sản phẩm đã sẵn sàng mở rộng quy mô toàn cầu cho hàng triệu người dùng và đạt hiệu quả tài chính bền vững' (mẫu 20 người dùng thân thiết có thiên kiến tích cực và kích thước mẫu quá nhỏ).
+3. Giai đoạn 3: Đánh giá Trực tuyến Thực tế (Sau thử nghiệm - Post-launch Online Monitoring)
+- Phương pháp: Theo dõi telemetry liên tục: tỷ lệ chỉnh sửa (Edit Rate), tỷ lệ hủy bỏ (Abandonment Rate), và độ trễ P95 trên toàn bộ lưu lượng sản phẩm.
+- Mục đích: Xác nhận tính ổn định dài hạn và giá trị kinh doanh thực tế của tính năng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chuỗi đánh giá sản phẩm AI phải tuân thủ trình tự phân tầng: Offline Benchmark -&gt; Controlled Canary Pilot -&gt; Online Telemetry. Mỗi giai đoạn sở hữu một ranh giới kết luận nghiêm ngặt; việc nhảy cóc từ kết quả offline test tốt để tuyên bố thành công trên thị trường là sai lầm nguy hiểm nhất của người làm sản phẩm AI.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Principles - Progressive Rollouts &amp; Anthropic Model Evaluation Best Practices (https://docs.anthropic.com/en/docs/build-with-claude/prompt-engineering)</t>
         </is>
       </c>
     </row>
@@ -963,10 +1026,34 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tính chi phí trên mỗi kết quả trước rồi nhân số lượt dùng; giữ nguyên chi phí công cụ và kiểm tra khi chỉ ngữ cảnh thay đổi.
-Phân tích theo nguyên lý thiết kế: Tính chi phí trên mỗi kết quả trước rồi nhân số lượt dùng; giữ nguyên chi phí công cụ và kiểm tra khi chỉ ngữ cảnh thay đổi.</t>
+- 1.0 điểm: Tính chính xác chi phí trên 1 kết quả (0,11 USD) và tổng chi phí hàng tháng hiện tại (5.500 USD).
+- 1.0 điểm: Trình bày chi tiết cơ cấu phân bổ chi phí (Inference: 3.000$, Tool: 500$, Review: 2.000$).
+- 1.0 điểm: Xác định đúng yếu tố chi phối lớn nhất là chi phí suy luận (Inference chiếm 54,55%).
+- 1.0 điểm: Tính chính xác chi phí mới khi suy luận tăng gấp đôi (0,17$/kết quả, tổng 8.500$/tháng, tăng thêm 3.000$). 
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Chi phí Biến đổi Hàng tháng (Monthly Variable Cost Calculation):
+- Chi phí cho 1 kết quả đầu ra đơn lẻ (Cost per Single Output):
+  + Chi phí suy luận của mô hình (Inference): 2 lần suy luận * 0,03 USD/lần = 0,06 USD.
+  + Chi phí gọi công cụ (Tool Calling): 1 lần * 0,01 USD = 0,01 USD.
+  + Chi phí kiểm tra thủ công của con người (Human Review): 5% xác suất * 0,80 USD = 0,04 USD.
+  -&gt; Tổng chi phí biến đổi trên 1 kết quả = 0,06 + 0,01 + 0,04 = 0,11 USD / kết quả.
+- Tổng chi phí biến đổi cho quy mô 50.000 kết quả / tháng:
+  + Tổng chi phí = 50.000 * 0,11 USD = 5.500 USD / tháng.
+- Cơ cấu chi phí phân bổ:
+  + Suy luận mô hình: 50.000 * 0,06 = 3.000 USD (chiếm 54,55%).
+  + Gọi công cụ: 50.000 * 0,01 = 500 USD (chiếm 9,09%).
+  + Kiểm tra thủ công: 50.000 * 0,04 = 2.000 USD (chiếm 36,36%).
+2. Yếu tố chi phối lớn nhất (Dominant Cost Driver):
+- Chi phí suy luận của mô hình (Model Inference Cost) là yếu tố chi phối lớn nhất, chiếm 54,55% tổng ngân sách hàng tháng (3.000 USD), theo sát sau đó là chi phí kiểm tra thủ công (36,36%).
+3. Tác động nếu ngữ cảnh làm chi phí suy luận tăng gấp đôi:
+- Giả định: Ngữ cảnh mở rộng khiến giá suy luận tăng gấp đôi (từ 0,03 lên 0,06 USD/lần, tức chi phí suy luận cho 1 kết quả tăng từ 0,06 lên 0,12 USD). Chi phí công cụ và kiểm tra thủ công giữ nguyên.
+- Chi phí mới cho 1 kết quả = 0,12 (suy luận) + 0,01 (công cụ) + 0,04 (kiểm tra) = 0,17 USD / kết quả.
+- Tổng chi phí biến đổi hàng tháng mới = 50.000 * 0,17 USD = 8.500 USD / tháng.
+- Tác động tài chính: Ngân sách tăng thêm đúng 3.000 USD/tháng (mức tăng +54,55% so với tổng chi phí ban đầu), và tỷ trọng chi phí suy luận lúc này sẽ tăng vọt lên chiếm 70,59% (6.000 / 8.500 USD) tổng cơ cấu chi phí sản phẩm.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hiểu rõ kinh tế học trên từng lượt sử dụng (Per-use Unit Economics) là năng lực bắt buộc của AI Product Manager. Chi phí suy luận LLM phụ thuộc tuyến tính vào độ dài context window. Việc mở rộng context bừa bãi có thể làm tăng gấp đôi chi phí suy luận và phá hủy hoàn toàn biên lợi nhuận của sản phẩm SaaS nếu không có chiến lược caching và context compaction.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Unit Economics in AI Products (A16Z AI Canon) &amp; Cloud Cost Optimization for LLM Inference (https://a16z.com/the-new-business-of-ai/)</t>
         </is>
       </c>
     </row>
@@ -1050,10 +1137,23 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giá trị và hậu quả có thể biện minh cho chi phí cao hơn nếu có bước kiểm tra.
-Phân tích theo nguyên lý thiết kế: Giá trị và hậu quả có thể biện minh cho chi phí cao hơn nếu có bước kiểm tra.</t>
+- 1.0 điểm: Chọn chính xác ưu tiên số 1 là Năng lực &amp; Độ chính xác của mô hình kèm lập luận về rủi ro pháp lý.
+- 1.0 điểm: Xác định đúng khía cạnh đánh đổi là Tốc độ (chấp nhận chờ 45s) và Chi phí suy luận.
+- 1.0 điểm: Đề xuất biện pháp giảm rủi ro 1: hiển thị trích dẫn nguồn luật và duyệt từng điều khoản (Human-in-the-loop).
+- 1.0 điểm: Đề xuất biện pháp giảm rủi ro 2: kiểm định độc lập đa mô hình (Dual-model audit guardrail).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Thứ tự Ưu tiên (Priority Selection):
+- Ưu tiên SỐ 1: Năng lực &amp; Độ chính xác Tuyệt đối (Model Capability &amp; Accuracy). Lý do: Trong lĩnh vực pháp lý, sai số hợp đồng gây ra thiệt hại tài chính và pháp lý cực kỳ đắt đỏ, trong khi việc soạn thảo thành công giúp tiết kiệm tới 2 giờ làm việc của luật sư (giá trị rất cao). Do đó, chất lượng và độ chuẩn xác pháp lý phải được đặt lên hàng đầu.
+2. Khía cạnh bắt buộc phải Đánh đổi (Trade-off Aspect):
+- Đánh đổi: Tốc độ / Thời gian phản hồi (Speed / Latency) và Chi phí trên từng lượt suy luận (Cost per Inference).
+- Biện minh: Khách hàng (luật sư) hoàn toàn chấp nhận chờ 45 giây để nhận được một văn bản chuẩn xác tiết kiệm 2 giờ làm việc. Với quy mô nhỏ (200 lần/tháng), tổng chi phí API dù dùng mô hình đắt nhất (như GPT-4o / Claude 3.5 Sonnet với chuỗi suy luận sâu) cũng chỉ tốn vài chục USD/tháng, hoàn toàn không đáng kể so với giá trị kinh tế tạo ra.
+3. Hai Biện pháp Giảm thiểu Rủi ro Pháp lý (Risk Mitigation Strategies):
+- Biện pháp 1: Thiết kế Cơ chế Kiểm tra Đối chiếu Song ngữ cảnh bắt buộc (Mandatory Legal Clause Citation &amp; Diff View): Mọi điều khoản do AI soạn thảo phải đi kèm trích dẫn chính xác điều luật hoặc hợp đồng mẫu đối chiếu; giao diện hiển thị bảng so sánh chi tiết và bắt buộc luật sư phải bấm 'Duyệt từng điều khoản' thay vì duyệt toàn bộ.
+- Biện pháp 2: Tích hợp Rào chắn Kiểm định Tự động Đa tầng (Dual-Model Independent Audit Guardrail): Sử dụng một mô hình thứ hai độc lập đóng vai trò 'Luật sư phản biện' (Adversarial Critic) để rà soát toàn bộ hợp đồng vừa soạn thảo nhằm phát hiện các mâu thuẫn pháp lý, điều khoản mơ hồ hoặc thiếu sót điều kiện bồi thường trước khi bàn giao cho người dùng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Ma trận định vị Chi phí - Năng lực - Tốc độ (Cost vs Capability vs Speed) trong sản phẩm AI luôn đòi hỏi sự đánh đổi có chủ đích. Với các sản phẩm High-Stakes (rủi ro cao, giá trị cao, tần suất thấp như soạn thảo hợp đồng), chiến lược tối ưu luôn là hy sinh tốc độ (chấp nhận 45s) và chi phí để tối đa hóa năng lực mô hình, kết hợp với các cơ chế kiểm định pháp lý độc lập.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - High-Stakes AI Systems &amp; Legal AI Product Design Standards (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -1136,10 +1236,31 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ cùng công thức cho ba hàng; chỉ thay các giả định đã nêu.
-Phân tích theo nguyên lý thiết kế: Giữ cùng công thức cho ba hàng; chỉ thay các giả định đã nêu.</t>
+- 1.0 điểm: Tính toán chính xác lợi ích ròng cho cả 3 kịch bản: Thận trọng (-500$), Cơ sở (+750$), Lạc quan (+1.650$).
+- 1.0 điểm: Giữ nguyên vẹn cấu trúc công thức đồng nhất giữa 3 hàng tính toán.
+- 1.0 điểm: Phân tích chính xác yếu tố chi phối (tỷ lệ chấp nhận và chi phí mỗi lượt) kèm phân tích điểm hòa vốn.
+- 1.0 điểm: Đưa ra tiêu chí dừng dự án (Kill Criterion) rõ ràng, có thời hạn và ngưỡng số đo lường dứt khoát.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Bảng Tính toán Lợi ích Ròng theo Ba Kịch bản cho 2.000 Yêu cầu/tháng:
+1. Bảng Tính toán Chi tiết:
+- Công thức chung cho từng kịch bản:
+  + Số kết quả được chấp nhận = 2.000 * Tỷ lệ chấp nhận.
+  + Tổng lợi ích tạo ra = Số kết quả được chấp nhận * 1,50 USD.
+  + Tổng chi phí vận hành = 2.000 * Chi phí mỗi yêu cầu.
+  + Lợi ích ròng (Net Benefit) = Tổng lợi ích - Tổng chi phí.
+| Kịch bản | Tỷ lệ chấp nhận | Số KQ chấp nhận | Tổng Lợi ích ($) | Chi phí/yêu cầu ($) | Tổng Chi phí ($) | Lợi ích Ròng ($) |
+| :--- | :---: | :---: | :---: | :---: | :---: | :---: |
+| **Thận trọng (Conservative)** | 30% | 600 | 600 * 1,50 = 900 USD | 0,70 USD | 2.000 * 0,70 = 1.400 USD | **-500 USD (LỖ)** |
+| **Cơ sở (Base Case)** | 55% | 1.100 | 1.100 * 1,50 = 1.650 USD | 0,45 USD | 2.000 * 0,45 = 900 USD | **+750 USD (LÃI)** |
+| **Lạc quan (Optimistic)** | 75% | 1.500 | 1.500 * 1,50 = 2.250 USD | 0,30 USD | 2.000 * 0,30 = 600 USD | **+1.650 USD (LÃI)** |
+2. Yếu tố thay đổi chi phối lợi ích ròng (Key Sensitivity Drivers):
+- Hai yếu tố tương tác quyết định điểm hòa vốn: Tỷ lệ chấp nhận của người dùng (User Acceptance Rate) và Đơn giá chi phí trên mỗi yêu cầu (Cost per Request). Ở kịch bản cơ sở, điểm hòa vốn (Break-even Acceptance Rate) là: `(2.000 * 0,45$) / (2.000 * 1,50$) = 30%`. Nếu tỷ lệ chấp nhận giảm dưới 30% ở mức chi phí 0,45$ (hoặc dưới 46,7% ở mức chi phí 0,70$), tính năng sẽ gây lỗ ròng cho công ty.
+3. Một Tiêu chí Dừng rõ ràng (Kill / Stop Criterion):
+- Tiêu chí dừng dứt khoát: 'Nếu sau 60 ngày thử nghiệm thực tế với người dùng, Tỷ lệ chấp nhận thực tế trung bình của tính năng đạt dưới 40% (khiến lợi ích ròng âm hoặc cận kề mức lỗ), hoặc Chi phí thực tế trên mỗi yêu cầu vượt quá 0,60 USD mà không có lộ trình tối ưu hóa prompt/cache khả thi, dự án sẽ lập tức bị DỪNG TRIỂN KHAI để bảo toàn vốn'.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Lập luận kịch bản ROI (ROI Scenario Reasoning) là công cụ phòng vệ tài chính thiết yếu để đánh giá tính khả thi thương mại của tính năng AI. Một kịch bản AI không bao giờ được xây dựng trên một con số màu hồng duy nhất mà phải có kịch bản xấu (Conservative) để thấy rõ rủi ro thâm hụt và thiết lập tiêu chí dừng (Kill Criterion) bảo vệ ngân sách doanh nghiệp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Harvard Business Review - Scenario Planning for High-Uncertainty Technology Projects &amp; Financial Modeling for AI Products (https://hbr.org/2013/05/living-in-the-futures)</t>
         </is>
       </c>
     </row>
